--- a/hairdresser_forms/031_hair_volumizing_powder_application_consent_form--hairdresser_forms.xlsx
+++ b/hairdresser_forms/031_hair_volumizing_powder_application_consent_form--hairdresser_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -876,8 +876,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -905,12 +905,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'clientname'}</t>
+          <t>clientname</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'ClientName'}</t>
+          <t>ClientName</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'clientage'}</t>
+          <t>clientage</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'ClientAge'}</t>
+          <t>ClientAge</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'clientaddress'}</t>
+          <t>clientaddress</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'ClientAddress'}</t>
+          <t>ClientAddress</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'haircut'}</t>
+          <t>haircut</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Haircut'}</t>
+          <t>Haircut</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'haircoloring'}</t>
+          <t>haircoloring</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'HairColoring'}</t>
+          <t>HairColoring</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'hairdyeing'}</t>
+          <t>hairdyeing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'HairDyeing'}</t>
+          <t>HairDyeing</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'dusting'}</t>
+          <t>dusting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Dusting'}</t>
+          <t>Dusting</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'blowing'}</t>
+          <t>blowing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Blowing'}</t>
+          <t>Blowing</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'brushing'}</t>
+          <t>brushing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Brushing'}</t>
+          <t>Brushing</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'natural'}</t>
+          <t>natural</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Natural'}</t>
+          <t>Natural</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'bold'}</t>
+          <t>bold</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Bold'}</t>
+          <t>Bold</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'pastel'}</t>
+          <t>pastel</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Pastel'}</t>
+          <t>Pastel</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'light'}</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Light'}</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'heavy'}</t>
+          <t>heavy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Heavy'}</t>
+          <t>Heavy</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'signature'}</t>
+          <t>signature</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Signature'}</t>
+          <t>Signature</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'stamp'}</t>
+          <t>stamp</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Stamp'}</t>
+          <t>Stamp</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'mr'}</t>
+          <t>mr</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Mr'}</t>
+          <t>Mr</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'mrs'}</t>
+          <t>mrs</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Mrs'}</t>
+          <t>Mrs</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'ms'}</t>
+          <t>ms</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Ms'}</t>
+          <t>Ms</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'january'}</t>
+          <t>january</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'January'}</t>
+          <t>January</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'february'}</t>
+          <t>february</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'February'}</t>
+          <t>February</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'march'}</t>
+          <t>march</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'March'}</t>
+          <t>March</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'april'}</t>
+          <t>april</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'April'}</t>
+          <t>April</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'may'}</t>
+          <t>may</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'May'}</t>
+          <t>May</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'june'}</t>
+          <t>june</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'June'}</t>
+          <t>June</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'july'}</t>
+          <t>july</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'July'}</t>
+          <t>July</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'august'}</t>
+          <t>august</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'August'}</t>
+          <t>August</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'september'}</t>
+          <t>september</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'September'}</t>
+          <t>September</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'october'}</t>
+          <t>october</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'October'}</t>
+          <t>October</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'november'}</t>
+          <t>november</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'November'}</t>
+          <t>November</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'december'}</t>
+          <t>december</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'December'}</t>
+          <t>December</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_9}</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 9}</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_10}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 10}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1653,12 +1653,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_11}</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 11}</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_12}</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 12}</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_13}</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 13}</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_14}</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 14}</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_15}</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 15}</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_16}</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 16}</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_17}</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 17}</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1772,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_18}</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 18}</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_19}</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 19}</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_20}</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 20}</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_21}</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 21}</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_22}</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': 22}</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1857,12 +1857,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_23}</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': 23}</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_24}</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 24}</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_25}</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': 25}</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'label':_26}</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'label': 26}</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'label':_27}</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'label': 27}</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'label':_28}</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'label': 28}</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1959,12 +1959,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'label':_29}</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'label': 29}</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1976,12 +1976,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'label':_30}</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'label': 30}</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -1993,12 +1993,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'label':_31}</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'label': 31}</t>
+          <t>31</t>
         </is>
       </c>
     </row>
